--- a/artfynd/A 6236-2021 artfynd.xlsx
+++ b/artfynd/A 6236-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6236-2021 artfynd.xlsx
+++ b/artfynd/A 6236-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,6 +1149,220 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123424582</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98391</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ivartjärnens S strand 150 m S om i blandskog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>392312</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7027207</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19D6a11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123424591</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97324</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ivartjärnens S strand 150 m S om i blandskog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>392312</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7027207</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1993-07-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19D6a11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6236-2021 artfynd.xlsx
+++ b/artfynd/A 6236-2021 artfynd.xlsx
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123424582</v>
+        <v>123424591</v>
       </c>
       <c r="B6" t="n">
-        <v>98391</v>
+        <v>97324</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123424591</v>
+        <v>123424582</v>
       </c>
       <c r="B7" t="n">
-        <v>97324</v>
+        <v>98391</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 6236-2021 artfynd.xlsx
+++ b/artfynd/A 6236-2021 artfynd.xlsx
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123424591</v>
+        <v>123424582</v>
       </c>
       <c r="B6" t="n">
-        <v>97324</v>
+        <v>98397</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123424582</v>
+        <v>123424591</v>
       </c>
       <c r="B7" t="n">
-        <v>98391</v>
+        <v>97330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 6236-2021 artfynd.xlsx
+++ b/artfynd/A 6236-2021 artfynd.xlsx
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123424591</v>
+        <v>123424582</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>98417</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123424582</v>
+        <v>123424591</v>
       </c>
       <c r="B7" t="n">
-        <v>98400</v>
+        <v>97350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 6236-2021 artfynd.xlsx
+++ b/artfynd/A 6236-2021 artfynd.xlsx
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123424582</v>
+        <v>123424591</v>
       </c>
       <c r="B6" t="n">
-        <v>98417</v>
+        <v>97367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123424591</v>
+        <v>123424582</v>
       </c>
       <c r="B7" t="n">
-        <v>97350</v>
+        <v>98523</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/artfynd/A 6236-2021 artfynd.xlsx
+++ b/artfynd/A 6236-2021 artfynd.xlsx
@@ -1154,7 +1154,7 @@
         <v>123424591</v>
       </c>
       <c r="B6" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>123424582</v>
       </c>
       <c r="B7" t="n">
-        <v>98523</v>
+        <v>98525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
